--- a/results/feature_selection/global/wnp/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global/wnp/rP_calc/metrics_global.xlsx
@@ -488,46 +488,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, I, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, I, Plag1, X_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4844802002200376</v>
+        <v>0.9639389024036521</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03512549066542439</v>
+        <v>0.01594125319468544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01128628560024415</v>
+        <v>0.0008019032312773486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1062369314327374</v>
+        <v>0.02831789595427861</v>
       </c>
       <c r="H2" t="n">
-        <v>747.8804856924364</v>
+        <v>167.0267249837179</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1650563398541597</v>
+        <v>0.01337966154079852</v>
       </c>
       <c r="J2" t="n">
-        <v>-555.0050362097047</v>
+        <v>-875.9368044624733</v>
       </c>
       <c r="K2" t="n">
-        <v>-540.8236266749474</v>
+        <v>-864.6556782000532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -535,155 +535,155 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4591252849290072</v>
+        <v>0.9598088368950778</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04206176814003169</v>
+        <v>0.01377674268603238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01184138128321639</v>
+        <v>0.0008937449415265747</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1088181110073888</v>
+        <v>0.02989556725547409</v>
       </c>
       <c r="H3" t="n">
-        <v>433.7275547253949</v>
+        <v>392.3642172592769</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1720513814195493</v>
+        <v>0.01418297039054527</v>
       </c>
       <c r="J3" t="n">
-        <v>-552.9555292310212</v>
+        <v>-864.4911753515074</v>
       </c>
       <c r="K3" t="n">
-        <v>-544.4466835101667</v>
+        <v>-856.0303306546923</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3623166556317099</v>
+        <v>0.9593977529587796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06624646919107849</v>
+        <v>0.01395110629588469</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01396081459942231</v>
+        <v>0.0009028863586995543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1181558910906363</v>
+        <v>0.03004806747029756</v>
       </c>
       <c r="H4" t="n">
-        <v>362.141959886854</v>
+        <v>402.6737728242416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2020775735300827</v>
+        <v>0.01431269456345581</v>
       </c>
       <c r="J4" t="n">
-        <v>-534.2091047004808</v>
+        <v>-863.2293187743055</v>
       </c>
       <c r="K4" t="n">
-        <v>-528.5365408865779</v>
+        <v>-854.7684740774904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2953684112637696</v>
+        <v>0.9582837475211996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06503762108914926</v>
+        <v>0.01434123436322045</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01542651389301689</v>
+        <v>0.0009276588869807347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1242035180380044</v>
+        <v>0.03045749311714171</v>
       </c>
       <c r="H5" t="n">
-        <v>1223.862680033876</v>
+        <v>421.6348662690142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.224688036345981</v>
+        <v>0.01466423696452664</v>
       </c>
       <c r="J5" t="n">
-        <v>-515.6301136426231</v>
+        <v>-859.8729624580926</v>
       </c>
       <c r="K5" t="n">
-        <v>-501.4487041078657</v>
+        <v>-851.4121177612775</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, I, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2447174447172652</v>
+        <v>0.9163479876793995</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06347555385127654</v>
+        <v>0.02092852762852638</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01653541654741787</v>
+        <v>0.001860199035914418</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1285901106128223</v>
+        <v>0.04313002476134715</v>
       </c>
       <c r="H6" t="n">
-        <v>851.2597863561375</v>
+        <v>522.0820504138919</v>
       </c>
       <c r="I6" t="n">
-        <v>0.239659558168013</v>
+        <v>0.02839774302132024</v>
       </c>
       <c r="J6" t="n">
-        <v>-510.8835933666197</v>
+        <v>-771.596901764811</v>
       </c>
       <c r="K6" t="n">
-        <v>-502.3747476457653</v>
+        <v>-760.3157755023909</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -691,77 +691,77 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2446757826513184</v>
+        <v>0.9152551064980523</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06343947349132943</v>
+        <v>0.02011265398687115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0165363286558862</v>
+        <v>0.001884501816726427</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1285936571370696</v>
+        <v>0.04341084906709873</v>
       </c>
       <c r="H7" t="n">
-        <v>850.9264142651245</v>
+        <v>259.3644317764088</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2396726952637249</v>
+        <v>0.02824261932229281</v>
       </c>
       <c r="J7" t="n">
-        <v>-510.8766432848304</v>
+        <v>-771.9873808714335</v>
       </c>
       <c r="K7" t="n">
-        <v>-502.367797563976</v>
+        <v>-763.5265361746184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2442942906787732</v>
+        <v>0.7759659691160989</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0632996786919062</v>
+        <v>0.02826629198338416</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0165446806675028</v>
+        <v>0.004981923048844859</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1286261274683445</v>
+        <v>0.07058273902906333</v>
       </c>
       <c r="H8" t="n">
-        <v>850.6498586484067</v>
+        <v>1097.556805203603</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2397929892636201</v>
+        <v>0.07119755539936172</v>
       </c>
       <c r="J8" t="n">
-        <v>-510.813020468745</v>
+        <v>-655.4404742040869</v>
       </c>
       <c r="K8" t="n">
-        <v>-502.3041747478906</v>
+        <v>-652.6201926384819</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,71 +769,71 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.002483196970466839</v>
+        <v>0.7527546537674743</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05987884585557444</v>
+        <v>0.02862851509492161</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02194738529011641</v>
+        <v>0.005498081181040611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1481464994190427</v>
+        <v>0.07414904706765024</v>
       </c>
       <c r="H9" t="n">
-        <v>2296.754723277296</v>
+        <v>912.3541552541481</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6332162575884431</v>
+        <v>0.07852226069648614</v>
       </c>
       <c r="J9" t="n">
-        <v>-479.2075157346925</v>
+        <v>-643.21615934991</v>
       </c>
       <c r="K9" t="n">
-        <v>-476.371233827741</v>
+        <v>-640.395877784305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P, T, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05258715052869567</v>
+        <v>0.7365723037989933</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04596346378229189</v>
+        <v>0.03817351948187587</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02304431217789241</v>
+        <v>0.005857933753323379</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1518035315066563</v>
+        <v>0.07653713969912501</v>
       </c>
       <c r="H10" t="n">
-        <v>754.6038654924013</v>
+        <v>1803.228994338349</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6648143273662669</v>
+        <v>0.08462886248762838</v>
       </c>
       <c r="J10" t="n">
-        <v>-473.0623738211661</v>
+        <v>-631.3548340848316</v>
       </c>
       <c r="K10" t="n">
-        <v>-470.2260919142146</v>
+        <v>-622.8939893880165</v>
       </c>
     </row>
   </sheetData>
